--- a/stories/arbres/ATOM-REL.AMI.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Anouk joue à la dinette dans le salon. Les assiettes en bois claquent. Papa plie le linge. Nina arrive. Anouk dit : tu veux jouer avec nous ? C'est inviter. Nina dit : non. Anouk sent un petit creux. Papa dit : un non est possible. On peut inviter. On accepte un non. Anouk dit : d'accord. Elle reprend une tasse. La tasse est lisse. Plus tard, Nina joue aux cubes. Anouk ne insiste pas. Elle accepte le non. Papa sourit. Anouk invite encore papa. Papa dit oui. Ils versent le thé imaginaire. Inviter, c'est demander. Un non, on l'accepte. Anouk souffle. Le creux se desserre.</t>
+          <t>Anouk joue à la dinette dans le salon. Les assiettes en bois claquent. Papa plie le linge. Nina arrive. Tu veux jouer avec nous ? C'est inviter. Non. Anouk sent un petit creux. Un non est possible. On peut inviter. On accepte un non. D'accord. Elle reprend une tasse. La tasse est lisse. Plus tard, Nina joue aux cubes. Anouk ne insiste pas. Elle accepte le non. Papa sourit. Anouk invite encore papa. Papa dit oui. Ils versent le thé imaginaire. Inviter, c'est demander. Un non, on l'accepte. Anouk souffle. Le creux se desserre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Anouk joue à la dinette dans le salon. Les assiettes en bois claquent. Papa plie le linge. Nina arrive.
+enfant-m|Tu veux jouer avec nous ? C'est inviter.
+copine|Non.
+narrateur|Anouk sent un petit creux.
+papa|Un non est possible. On peut inviter. On accepte un non.
+enfant-m|D'accord. Elle reprend une tasse.
+narrateur|La tasse est lisse. Plus tard, Nina joue aux cubes. Anouk ne insiste pas. Elle accepte le non. Papa sourit. Anouk invite encore papa. Papa dit oui. Ils versent le thé imaginaire. Inviter, c'est demander. Un non, on l'accepte. Anouk souffle. Le creux se desserre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nina dit non. Que fait Anouk ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Anouk a invité. Nina a dit non. Anouk a accepté le non. Puis papa a joué.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Anouk range une tasse. Papa plie la dernière serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|La tasse est lisse. Plus tard, Nina joue aux cubes. Anouk ne insiste pas. Elle accepte le non. Papa sourit. Anouk invite encore papa. Papa dit oui. Ils versent le thé imaginaire. Inviter, c'est demander. Un non, on l'accepte. Anouk souffle. Le creux se desserre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Nina dit non. Que fait Anouk ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Anouk a invité. Nina a dit non. Anouk a accepté le non. Puis papa a joué.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Anouk range une tasse. Papa plie la dernière serviette.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anouk invite à la dinette</t>
+          <t>Le thé de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou invite Nina à la dinette. Nina dit non. Chouchou accepte et verse le thé avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Anouk joue à la dinette dans le salon. Les assiettes en bois claquent. Papa plie le linge. Nina arrive. Tu veux jouer avec nous ? C'est inviter. Non. Anouk sent un petit creux. Un non est possible. On peut inviter. On accepte un non. D'accord. Elle reprend une tasse. La tasse est lisse. Plus tard, Nina joue aux cubes. Anouk ne insiste pas. Elle accepte le non. Papa sourit. Anouk invite encore papa. Papa dit oui. Ils versent le thé imaginaire. Inviter, c'est demander. Un non, on l'accepte. Anouk souffle. Le creux se desserre.</t>
+          <t>Une vapeur de soupe entre dans le salon. Elle sent la carotte et le thym. Les assiettes en bois sont empilées. Elles font un petit tas clair. Une chaussette dépasse du linge. Le rideau bouge près de la fenêtre. Chouchou, tu as senti la soupe ? Oui, papa. Ça sent bon. Je plie le linge. Toi, tu as la dinette. En ce moment, Chouchou pose une tasse. La tasse est lisse et ronde. Une assiette claque contre une autre. Je verse le thé. Le thé imaginaire, d'accord. Nina arrive dans le salon. Elle a un cube bleu dans la main. Le cube est un peu luisant. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Nina secoue la tête. Non. Chouchou sent un petit creux. La tasse reste dans ses doigts. Papa pose une serviette. Un non est possible. On peut inviter. On accepte un non. D'accord. Chouchou reprend la tasse. Il verse encore le thé imaginaire. La tasse tapote l'assiette. Tu verses tout doux. C'est pour papa. Merci. Je goûte. Il est tiède, ce thé. Nina s'assoit près des cubes. Les cubes cliquent sur le tapis. Chouchou accepte le non. Il pose une petite cuillère. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, on l'accepte. On continue la dinette ? Oui, papa. Le rideau bouge encore. La soupe sent toujours bon. Tu as fini de verser ? Oui. Bravo. Tu as fait du bon travail. Chouchou souffle. Le creux se desserre un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Anouk joue à la dinette dans le salon. Les assiettes en bois claquent. Papa plie le linge. Nina arrive.
-enfant-m|Tu veux jouer avec nous ? C'est inviter.
+          <t>narrateur|Une vapeur de soupe entre dans le salon.
+narrateur|Elle sent la carotte et le thym.
+narrateur|Les assiettes en bois sont empilées.
+narrateur|Elles font un petit tas clair.
+narrateur|Une chaussette dépasse du linge.
+narrateur|Le rideau bouge près de la fenêtre.
+papa|Chouchou, tu as senti la soupe ?
+enfant-m|Oui, papa.
+enfant-m|Ça sent bon.
+papa|Je plie le linge.
+papa|Toi, tu as la dinette.
+narrateur|En ce moment, Chouchou pose une tasse.
+narrateur|La tasse est lisse et ronde.
+narrateur|Une assiette claque contre une autre.
+enfant-m|Je verse le thé.
+papa|Le thé imaginaire, d'accord.
+narrateur|Nina arrive dans le salon.
+narrateur|Elle a un cube bleu dans la main.
+narrateur|Le cube est un peu luisant.
+papa|Tu peux inviter.
+papa|Inviter, c'est demander.
+enfant-m|Tu veux jouer avec nous ?
+narrateur|Nina secoue la tête.
 copine|Non.
-narrateur|Anouk sent un petit creux.
-papa|Un non est possible. On peut inviter. On accepte un non.
-enfant-m|D'accord. Elle reprend une tasse.
-narrateur|La tasse est lisse. Plus tard, Nina joue aux cubes. Anouk ne insiste pas. Elle accepte le non. Papa sourit. Anouk invite encore papa. Papa dit oui. Ils versent le thé imaginaire. Inviter, c'est demander. Un non, on l'accepte. Anouk souffle. Le creux se desserre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Chouchou sent un petit creux.
+narrateur|La tasse reste dans ses doigts.
+narrateur|Papa pose une serviette.
+papa|Un non est possible.
+papa|On peut inviter.
+papa|On accepte un non.
+enfant-m|D'accord.
+narrateur|Chouchou reprend la tasse.
+narrateur|Il verse encore le thé imaginaire.
+narrateur|La tasse tapote l'assiette.
+papa|Tu verses tout doux.
+enfant-m|C'est pour papa.
+papa|Merci.
+papa|Je goûte.
+papa|Il est tiède, ce thé.
+narrateur|Nina s'assoit près des cubes.
+narrateur|Les cubes cliquent sur le tapis.
+narrateur|Chouchou accepte le non.
+narrateur|Il pose une petite cuillère.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+enfant-m|Elle a dit non.
+papa|Un non, on l'accepte.
+papa|On continue la dinette ?
+enfant-m|Oui, papa.
+narrateur|Le rideau bouge encore.
+narrateur|La soupe sent toujours bon.
+papa|Tu as fini de verser ?
+enfant-m|Oui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Chouchou souffle.
+narrateur|Le creux se desserre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nina dit non. Que fait Anouk ?</t>
+          <t>Nina dit non. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1563,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nina dit non. Que fait Anouk ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina dit non.
+narrateur|Que fait Chouchou ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Anouk a invité. Nina a dit non. Anouk a accepté le non. Puis papa a joué.</t>
+          <t>Chouchou a demandé. C'est inviter. Nina a dit non. Chouchou a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Chouchou. J'ai dit d'accord. Oui. Un non, c'est possible. La tasse lisse reste près de l'assiette. Les cubes de Nina sont sur le tapis. Tu as fini le thé ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1731,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Anouk a invité. Nina a dit non. Anouk a accepté le non. Puis papa a joué.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou a demandé.
+narrateur|C'est inviter.
+narrateur|Nina a dit non.
+narrateur|Chouchou a accepté le non.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+papa|Bravo, Chouchou.
+enfant-m|J'ai dit d'accord.
+papa|Oui.
+papa|Un non, c'est possible.
+narrateur|La tasse lisse reste près de l'assiette.
+narrateur|Les cubes de Nina sont sur le tapis.
+papa|Tu as fini le thé ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Anouk range une tasse. Papa plie la dernière serviette.</t>
+          <t>Chouchou range une tasse. L'assiette en bois claque doucement. Je plie la dernière serviette. La serviette est chaude encore. Elle sent la lessive. Oui. On met la tasse dans la boîte. Tu as fini de ranger la tasse ? Oui. La vapeur de soupe est plus fine. Le rideau ne bouge plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,10 +1907,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Anouk range une tasse. Papa plie la dernière serviette.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Chouchou range une tasse.
+narrateur|L'assiette en bois claque doucement.
+papa|Je plie la dernière serviette.
+narrateur|La serviette est chaude encore.
+enfant-m|Elle sent la lessive.
+papa|Oui.
+papa|On met la tasse dans la boîte.
+papa|Tu as fini de ranger la tasse ?
+enfant-m|Oui.
+narrateur|La vapeur de soupe est plus fine.
+narrateur|Le rideau ne bouge plus.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,7 +1944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Chouchou a invité. Il a accepté un non. La dinette est rangée. Bravo, Chouchou. On goûte la soupe ? Oui. On goûte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,10 +2084,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Chouchou a invité.
+narrateur|Il a accepté un non.
+narrateur|La dinette est rangée.
+papa|Bravo, Chouchou.
+enfant-m|On goûte la soupe ?
+papa|Oui.
+papa|On goûte.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une vapeur de soupe entre dans le salon. Elle sent la carotte et le thym. Les assiettes en bois sont empilées. Elles font un petit tas clair. Une chaussette dépasse du linge. Le rideau bouge près de la fenêtre. Chouchou, tu as senti la soupe ? Oui, papa. Ça sent bon. Je plie le linge. Toi, tu as la dinette. En ce moment, Chouchou pose une tasse. La tasse est lisse et ronde. Une assiette claque contre une autre. Je verse le thé. Le thé imaginaire, d'accord. Nina arrive dans le salon. Elle a un cube bleu dans la main. Le cube est un peu luisant. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Nina secoue la tête. Non. Chouchou sent un petit creux. La tasse reste dans ses doigts. Papa pose une serviette. Un non est possible. On peut inviter. On accepte un non. D'accord. Chouchou reprend la tasse. Il verse encore le thé imaginaire. La tasse tapote l'assiette. Tu verses tout doux. C'est pour papa. Merci. Je goûte. Il est tiède, ce thé. Nina s'assoit près des cubes. Les cubes cliquent sur le tapis. Chouchou accepte le non. Il pose une petite cuillère. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, on l'accepte. On continue la dinette ? Oui, papa. Le rideau bouge encore. La soupe sent toujours bon. Tu as fini de verser ? Oui. Bravo. Tu as fait du bon travail. Chouchou souffle. Le creux se desserre un peu.</t>
+          <t>Une vapeur de soupe entre dans le salon. Elle sent la carotte et le thym. Les assiettes en bois sont empilées. Elles font un petit tas clair. Une chaussette dépasse du linge. Le rideau bouge près de la fenêtre. Chouchou, tu as senti la soupe ? Oui, papa. Ça sent bon. Je plie le linge. Toi, tu as la dinette. En ce moment, Chouchou pose une tasse. La tasse est lisse et ronde. Une assiette claque contre une autre. Je verse le thé. Le thé imaginaire, d'accord. Nina arrive dans le salon. Elle a un cube bleu dans la main. Le cube est un peu luisant. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Nina secoue la tête. Non. Chouchou sent un petit creux. La tasse reste dans ses doigts. Papa pose une serviette. Un non est possible. On peut inviter. On accepte un non. D'accord. Chouchou reprend la tasse. Il verse encore le thé imaginaire. La tasse tapote l'assiette. Tu verses tout doux. C'est pour papa. Merci. Je goûte. Il est tiède, ce thé. Nina s'assoit près des cubes. Les cubes cliquent sur le tapis. Chouchou accepte le non. Il pose une petite cuillère. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, on l'accepte. On continue la dinette ? Oui, papa. Le rideau bouge encore. La soupe sent toujours bon. Tu as fini de verser ? Oui. Bravo. Chouchou souffle. Le creux se desserre un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Anouk joue à la dinette dans le salon. Les assiettes en bois claquent. Papa plie le linge. Nina arrive. Anouk dit : tu veux jouer avec nous ? C'est &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Nina dit : non. Anouk sent un petit creux. Papa dit : un non est possible. On peut inviter. On accepte un non. Anouk dit : d'accord. Elle reprend une tasse. La tasse est lisse. Plus tard, Nina joue aux cubes. Anouk ne insiste pas. Elle accepte le non. Papa sourit. Anouk invite encore papa. Papa dit oui. Ils versent le thé imaginaire. Inviter, c'est demander. Un non, on l'accepte. Anouk souffle. Le creux se desserre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une vapeur de soupe entre dans le salon. Elle sent la carotte et le thym. Les assiettes en bois sont empilées. Elles font un petit tas clair. Une chaussette dépasse du linge. Le rideau bouge près de la fenêtre. Chouchou, tu as senti la soupe ? Oui, papa. Ça sent bon. Je plie le linge. Toi, tu as la dinette. En ce moment, Chouchou pose une tasse. La tasse est lisse et ronde. Une assiette claque contre une autre. Je verse le thé. Le thé imaginaire, d'accord. Nina arrive dans le salon. Elle a un cube bleu dans la main. Le cube est un peu luisant. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Nina secoue la tête. Non. Chouchou sent un petit creux. La tasse reste dans ses doigts. Papa pose une serviette. Un non est possible. On peut inviter. On accepte un non. D'accord. Chouchou reprend la tasse. Il verse encore le thé imaginaire. La tasse tapote l'assiette. Tu verses tout doux. C'est pour papa. Merci. Je goûte. Il est tiède, ce thé. Nina s'assoit près des cubes. Les cubes cliquent sur le tapis. Chouchou accepte le non. Il pose une petite cuillère. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, on l'accepte. On continue la dinette ? Oui, papa. Le rideau bouge encore. La soupe sent toujours bon. Tu as fini de verser ? Oui. Bravo. Chouchou souffle. Le creux se desserre un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1378,7 +1378,6 @@
 papa|Tu as fini de verser ?
 enfant-m|Oui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Chouchou souffle.
 narrateur|Le creux se desserre un peu.</t>
         </is>
@@ -1412,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina dit non. Que fait Anouk ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina dit non. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1596,7 +1595,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Anouk a invité. Nina a dit non. Anouk a accepté le non. Puis papa a joué.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a demandé. C'est inviter. Nina a dit non. Chouchou a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Chouchou. J'ai dit d'accord. Oui. Un non, c'est possible. La tasse lisse reste près de l'assiette. Les cubes de Nina sont sur le tapis. Tu as fini le thé ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1776,7 +1775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Anouk range une tasse. Papa plie la dernière serviette.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou range une tasse. L'assiette en bois claque doucement. Je plie la dernière serviette. La serviette est chaude encore. Elle sent la lessive. Oui. On met la tasse dans la boîte. Tu as fini de ranger la tasse ? Oui. La vapeur de soupe est plus fine. Le rideau ne bouge plus.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1944,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a invité. Il a accepté un non. La dinette est rangée. Bravo, Chouchou. On goûte la soupe ? Oui. On goûte. L'histoire est finie.</t>
+          <t>Chouchou a invité. Il a accepté un non. La dinette est rangée. Bravo, Chouchou. On goûte la soupe ? Oui. On goûte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a invité. Il a accepté un non. La dinette est rangée. Bravo, Chouchou. On goûte la soupe ? Oui. On goûte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,8 +2089,7 @@
 papa|Bravo, Chouchou.
 enfant-m|On goûte la soupe ?
 papa|Oui.
-papa|On goûte.
-narrateur|L'histoire est finie.</t>
+papa|On goûte.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anouk, Nina, papa</t>
+          <t>Chouchou, Nina, papa</t>
         </is>
       </c>
     </row>
